--- a/sources/hwoarang_step6b.xlsx
+++ b/sources/hwoarang_step6b.xlsx
@@ -423,7 +423,7 @@
     <col width="78" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -4569,17 +4569,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4777,17 +4777,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">

--- a/sources/hwoarang_step6b.xlsx
+++ b/sources/hwoarang_step6b.xlsx
@@ -854,6 +854,11 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
@@ -906,6 +911,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
@@ -958,6 +968,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
@@ -1008,6 +1023,11 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>In RFF 2+5 throws don't work.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -9947,6 +9967,11 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
@@ -9977,6 +10002,11 @@
       <c r="K183" t="inlineStr">
         <is>
           <t>mhhLmmlhmh</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
